--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104529_W8.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104529_W8.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.4378</v>
+        <v>2.6502</v>
       </c>
       <c r="E2" t="n">
-        <v>2.2691</v>
+        <v>0.5841</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1688</v>
+        <v>2.0661</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0481</v>
+        <v>0.0298</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.8582</v>
+        <v>-0.8804999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9063</v>
+        <v>0.9103</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.227</v>
+        <v>-0.2587</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-0.9661999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>0.709</v>
+        <v>0.7075</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2751</v>
+        <v>0.2886</v>
       </c>
       <c r="N2" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.0857</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1973</v>
+        <v>0.2028</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R2" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S2" t="n">
-        <v>3.567</v>
+        <v>1.7977</v>
       </c>
       <c r="T2" t="n">
-        <v>2.7644</v>
+        <v>1.1191</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8027</v>
+        <v>0.6785</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8227</v>
+        <v>0.8228</v>
       </c>
       <c r="W2" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.27</v>
+        <v>-0.2667</v>
       </c>
     </row>
     <row r="3">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2996</v>
+        <v>2.5948</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0115</v>
+        <v>-0.0236</v>
       </c>
       <c r="F3" t="n">
-        <v>2.3111</v>
+        <v>2.6184</v>
       </c>
       <c r="G3" t="n">
-        <v>0.107</v>
+        <v>0.1105</v>
       </c>
       <c r="H3" t="n">
-        <v>0.88</v>
+        <v>0.8898</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.7731</v>
+        <v>-0.7793</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.435</v>
+        <v>-0.4506</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6927</v>
+        <v>0.6895</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.1276</v>
+        <v>-1.1401</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5419</v>
+        <v>0.5611</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1874</v>
+        <v>0.2003</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3546</v>
+        <v>0.3608</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1677</v>
+        <v>1.4551</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8771</v>
+        <v>0.8823</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2906</v>
+        <v>0.5729</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.1093</v>
+        <v>-0.1089</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1093</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Y. TRAORE</t>
+          <t>M. SPISSU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2882</v>
+        <v>0.4653</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8080000000000001</v>
+        <v>2.4466</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4802</v>
+        <v>-1.9812</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.6609</v>
+        <v>-2.5589</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6609</v>
+        <v>-1.0142</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>-1.5447</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.7864</v>
+        <v>-0.1674</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.7864</v>
+        <v>-0.3382</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.1708</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1255</v>
+        <v>-2.3915</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1255</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>-1.7155</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.1382</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.3658</v>
       </c>
       <c r="S4" t="n">
-        <v>1.7884</v>
+        <v>1.3413</v>
       </c>
       <c r="T4" t="n">
-        <v>1.4336</v>
+        <v>1.2074</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3548</v>
+        <v>0.1339</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1607</v>
+        <v>0.5447</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1607</v>
+        <v>1.6342</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. YUSTA</t>
+          <t>Y. TRAORE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2864</v>
+        <v>0.2509</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9716</v>
+        <v>-0.1396</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6852</v>
+        <v>0.3904</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.856</v>
+        <v>-0.6606</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0304</v>
+        <v>-0.6606</v>
       </c>
       <c r="I5" t="n">
-        <v>-3.8864</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.7331</v>
+        <v>-0.7896</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7406</v>
+        <v>-0.7896</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.4737</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.1229</v>
+        <v>0.129</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7103</v>
+        <v>0.129</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.4126</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.5878</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.4025</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8147</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.5163</v>
+        <v>0.7537</v>
       </c>
       <c r="T5" t="n">
-        <v>2.347</v>
+        <v>0.4923</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1693</v>
+        <v>0.2614</v>
       </c>
       <c r="V5" t="n">
-        <v>3.2138</v>
+        <v>0.1578</v>
       </c>
       <c r="W5" t="n">
-        <v>3.7602</v>
+        <v>0.1578</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5463</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5709</v>
+        <v>0.24</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.6453</v>
+        <v>-2.0751</v>
       </c>
       <c r="F6" t="n">
-        <v>2.0744</v>
+        <v>2.3151</v>
       </c>
       <c r="G6" t="n">
         <v>-0.0331</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5556</v>
+        <v>-0.5544</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5224</v>
+        <v>0.5213</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.4496</v>
+        <v>-0.4651</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9415</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4824</v>
+        <v>0.4764</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4165</v>
+        <v>0.432</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3764</v>
+        <v>0.3871</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R6" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4286</v>
+        <v>0.382</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8347</v>
+        <v>-0.2442</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4062</v>
+        <v>0.6262</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1093</v>
+        <v>-0.1089</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1093</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. SPISSU</t>
+          <t>S. YUSTA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.3645</v>
+        <v>-0.3724</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7472</v>
+        <v>0.2736</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.1118</v>
+        <v>-0.6461</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.5663</v>
+        <v>-3.8619</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.0203</v>
+        <v>0.0261</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.546</v>
+        <v>-3.888</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1447</v>
+        <v>-1.7718</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.3259</v>
+        <v>0.7165</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1812</v>
+        <v>-2.4883</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.4215</v>
+        <v>-2.0901</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6944</v>
+        <v>-0.6904</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.7272</v>
+        <v>-1.3997</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1342</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2268</v>
+        <v>-3.4145</v>
       </c>
       <c r="R7" t="n">
-        <v>1.361</v>
+        <v>1.8211</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4788</v>
+        <v>1.8859</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5202</v>
+        <v>1.7182</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0414</v>
+        <v>0.1677</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5463</v>
+        <v>3.197</v>
       </c>
       <c r="W7" t="n">
-        <v>1.639</v>
+        <v>3.7417</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0927</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. BELL-HAYNES</t>
+          <t>D. STEPHENS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.4961</v>
+        <v>-1.9628</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.7357</v>
+        <v>-0.6128</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2396</v>
+        <v>-1.35</v>
       </c>
       <c r="G8" t="n">
-        <v>2.1171</v>
+        <v>-3.4051</v>
       </c>
       <c r="H8" t="n">
-        <v>0.094</v>
+        <v>-0.3992</v>
       </c>
       <c r="I8" t="n">
-        <v>2.0231</v>
+        <v>-3.0059</v>
       </c>
       <c r="J8" t="n">
-        <v>1.9669</v>
+        <v>-0.8843</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5652</v>
+        <v>-0.1691</v>
       </c>
       <c r="L8" t="n">
-        <v>2.5321</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1502</v>
+        <v>-2.5209</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6592</v>
+        <v>-0.2301</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.509</v>
+        <v>-2.2907</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.9488</v>
+        <v>0.6829</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.9903</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0415</v>
+        <v>0.6829</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6303</v>
+        <v>0.7594</v>
       </c>
       <c r="T8" t="n">
-        <v>0.127</v>
+        <v>0.2715</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5032</v>
+        <v>0.4879</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.2946</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.4553</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B. DUBLJEVIC</t>
+          <t>T. BELL-HAYNES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.5962</v>
+        <v>-2.0936</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2016</v>
+        <v>-2.2505</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.7978</v>
+        <v>0.1569</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.713</v>
+        <v>2.1036</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8832</v>
+        <v>0.0838</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.5962</v>
+        <v>2.0198</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5036</v>
+        <v>1.9265</v>
       </c>
       <c r="K9" t="n">
-        <v>1.2153</v>
+        <v>-0.5903</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7117</v>
+        <v>2.5168</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.2166</v>
+        <v>0.1771</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3321</v>
+        <v>0.6741</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.8844</v>
+        <v>-0.497</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.2683</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.6293</v>
+        <v>-5.0079</v>
       </c>
       <c r="R9" t="n">
-        <v>1.361</v>
+        <v>2.0487</v>
       </c>
       <c r="S9" t="n">
-        <v>3.4098</v>
+        <v>1.0499</v>
       </c>
       <c r="T9" t="n">
-        <v>3.1666</v>
+        <v>0.6731</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2431</v>
+        <v>0.3768</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.0246</v>
+        <v>-2.2879</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.1853</v>
+        <v>-2.4457</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. STEPHENS</t>
+          <t>E. STEVENSON</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.6729</v>
+        <v>-2.4954</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4312</v>
+        <v>-2.5799</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2417</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.4091</v>
+        <v>-0.3261</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3997</v>
+        <v>-1.126</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.0094</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.8747</v>
+        <v>-0.2988</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.163</v>
+        <v>-1.5276</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7117</v>
+        <v>1.2288</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.5344</v>
+        <v>-0.0273</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2368</v>
+        <v>0.4016</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.2976</v>
+        <v>-0.4289</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6805</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-2.5039</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0556</v>
+        <v>0.8501</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5565</v>
+        <v>0.2228</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6121</v>
+        <v>0.6273</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.1984</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.1984</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E. STEVENSON</t>
+          <t>D. ROBINSON</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.3315</v>
+        <v>-3.1615</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2714</v>
+        <v>-2.8681</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0601</v>
+        <v>-0.2933</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.3288</v>
+        <v>-4.9604</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.1284</v>
+        <v>-3.4889</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7997</v>
+        <v>-1.4715</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2893</v>
+        <v>-3.7293</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.5208</v>
+        <v>-3.0142</v>
       </c>
       <c r="L11" t="n">
-        <v>1.2315</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0395</v>
+        <v>-1.231</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3923</v>
+        <v>-0.4747</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4318</v>
+        <v>-0.7563</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.8147</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.4952</v>
+        <v>-1.3658</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6805</v>
+        <v>1.3658</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0139</v>
+        <v>1.2542</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4869</v>
+        <v>0.9797</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5008</v>
+        <v>0.2744</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2019</v>
+        <v>0.5447</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2019</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. ROBINSON</t>
+          <t>B. DUBLJEVIC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.8092</v>
+        <v>-4.2976</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.6092</v>
+        <v>-1.4107</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2</v>
+        <v>-2.8869</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.9525</v>
+        <v>-1.7095</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.4759</v>
+        <v>0.8791</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.4767</v>
+        <v>-2.5886</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.6982</v>
+        <v>0.4807</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.9865</v>
+        <v>1.1958</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.7117</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.2543</v>
+        <v>-2.1902</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4894</v>
+        <v>-0.3168</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.7649</v>
+        <v>-1.8734</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.361</v>
+        <v>-3.6421</v>
       </c>
       <c r="R12" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S12" t="n">
-        <v>0.597</v>
+        <v>1.7094</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1966</v>
+        <v>1.5929</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4004</v>
+        <v>0.1165</v>
       </c>
       <c r="V12" t="n">
-        <v>0.5463</v>
+        <v>-2.0212</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2534</v>
+        <v>0.1578</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.7071</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.529300000000001</v>
+        <v>-8.1821</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.706799999999999</v>
+        <v>-8.656000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1775</v>
+        <v>0.4739000000000004</v>
       </c>
       <c r="G13" t="n">
-        <v>-15.2475</v>
+        <v>-15.2717</v>
       </c>
       <c r="H13" t="n">
-        <v>-6.2114</v>
+        <v>-6.245</v>
       </c>
       <c r="I13" t="n">
-        <v>-9.036299999999999</v>
+        <v>-9.0267</v>
       </c>
       <c r="J13" t="n">
-        <v>-6.1675</v>
+        <v>-6.408399999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>-5.5672</v>
+        <v>-5.7349</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.6002000000000001</v>
+        <v>-0.6737</v>
       </c>
       <c r="M13" t="n">
-        <v>-9.080000000000002</v>
+        <v>-8.863200000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.6444000000000001</v>
+        <v>-0.5100999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-8.435600000000001</v>
+        <v>-8.353</v>
       </c>
       <c r="P13" t="n">
-        <v>-5.6707</v>
+        <v>-5.6907</v>
       </c>
       <c r="Q13" t="n">
-        <v>-19.2808</v>
+        <v>-19.3487</v>
       </c>
       <c r="R13" t="n">
-        <v>13.61</v>
+        <v>13.658</v>
       </c>
       <c r="S13" t="n">
-        <v>12.8386</v>
+        <v>13.2387</v>
       </c>
       <c r="T13" t="n">
-        <v>8.513999999999999</v>
+        <v>8.915100000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>4.3246</v>
+        <v>4.3235</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.4499000000000011</v>
+        <v>-0.4583000000000002</v>
       </c>
       <c r="W13" t="n">
-        <v>8.227399999999999</v>
+        <v>8.186</v>
       </c>
       <c r="X13" t="n">
-        <v>-8.677199999999999</v>
+        <v>-8.6442</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.2195</v>
+        <v>4.4403</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2239</v>
+        <v>2.1917</v>
       </c>
       <c r="F14" t="n">
-        <v>1.9956</v>
+        <v>2.2486</v>
       </c>
       <c r="G14" t="n">
-        <v>3.7142</v>
+        <v>3.7197</v>
       </c>
       <c r="H14" t="n">
-        <v>2.3014</v>
+        <v>2.306</v>
       </c>
       <c r="I14" t="n">
-        <v>1.4127</v>
+        <v>1.4137</v>
       </c>
       <c r="J14" t="n">
-        <v>3.0736</v>
+        <v>3.0572</v>
       </c>
       <c r="K14" t="n">
-        <v>1.1704</v>
+        <v>1.1581</v>
       </c>
       <c r="L14" t="n">
-        <v>1.9032</v>
+        <v>1.8991</v>
       </c>
       <c r="M14" t="n">
-        <v>0.6405999999999999</v>
+        <v>0.6625</v>
       </c>
       <c r="N14" t="n">
-        <v>1.131</v>
+        <v>1.1479</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.4904</v>
+        <v>-0.4854</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R14" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.973</v>
+        <v>-0.7559</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3811</v>
+        <v>-0.3812</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5919</v>
+        <v>-0.3747</v>
       </c>
       <c r="V14" t="n">
-        <v>1.4783</v>
+        <v>1.4764</v>
       </c>
       <c r="W14" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.4289</v>
+        <v>3.7055</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2494</v>
+        <v>-0.269</v>
       </c>
       <c r="F15" t="n">
-        <v>3.6783</v>
+        <v>3.9745</v>
       </c>
       <c r="G15" t="n">
-        <v>1.1807</v>
+        <v>1.2011</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.9598</v>
+        <v>-0.9457</v>
       </c>
       <c r="I15" t="n">
-        <v>2.1405</v>
+        <v>2.1468</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.2654</v>
+        <v>-0.2802</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.1686</v>
+        <v>-2.1793</v>
       </c>
       <c r="L15" t="n">
-        <v>1.9032</v>
+        <v>1.8991</v>
       </c>
       <c r="M15" t="n">
-        <v>1.4461</v>
+        <v>1.4814</v>
       </c>
       <c r="N15" t="n">
-        <v>1.2088</v>
+        <v>1.2336</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2373</v>
+        <v>0.2477</v>
       </c>
       <c r="P15" t="n">
-        <v>3.4025</v>
+        <v>3.4145</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>3.4025</v>
+        <v>3.4145</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.0863</v>
+        <v>-1.8418</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0767</v>
+        <v>-1.0782</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.0096</v>
+        <v>-0.7635999999999999</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.7712</v>
+        <v>2.4484</v>
       </c>
       <c r="E16" t="n">
-        <v>2.4198</v>
+        <v>2.1592</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3513</v>
+        <v>0.2892</v>
       </c>
       <c r="G16" t="n">
-        <v>3.4793</v>
+        <v>3.4806</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.5239</v>
+        <v>-1.5168</v>
       </c>
       <c r="I16" t="n">
-        <v>5.0031</v>
+        <v>4.9974</v>
       </c>
       <c r="J16" t="n">
-        <v>2.3987</v>
+        <v>2.3731</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.1513</v>
+        <v>-2.1621</v>
       </c>
       <c r="L16" t="n">
-        <v>4.5499</v>
+        <v>4.5352</v>
       </c>
       <c r="M16" t="n">
-        <v>1.0806</v>
+        <v>1.1074</v>
       </c>
       <c r="N16" t="n">
-        <v>0.6274</v>
+        <v>0.6452</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4532</v>
+        <v>0.4622</v>
       </c>
       <c r="P16" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8157</v>
+        <v>-1.1507</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0212</v>
+        <v>-0.214</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8369</v>
+        <v>-0.9367</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="17">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.8946</v>
+        <v>1.7226</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2467</v>
+        <v>0.9591</v>
       </c>
       <c r="F17" t="n">
-        <v>0.648</v>
+        <v>0.7635</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1213</v>
+        <v>-0.137</v>
       </c>
       <c r="H17" t="n">
-        <v>3.2453</v>
+        <v>3.2373</v>
       </c>
       <c r="I17" t="n">
-        <v>-3.3666</v>
+        <v>-3.3743</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1976</v>
+        <v>0.1625</v>
       </c>
       <c r="K17" t="n">
-        <v>3.2311</v>
+        <v>3.2093</v>
       </c>
       <c r="L17" t="n">
-        <v>-3.0335</v>
+        <v>-3.0469</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3189</v>
+        <v>-0.2995</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0142</v>
+        <v>0.028</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3331</v>
+        <v>-0.3275</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5816</v>
+        <v>-0.7259</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0393</v>
+        <v>-0.1955</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6209</v>
+        <v>-0.5304</v>
       </c>
       <c r="V17" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="W17" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1813,37 +1813,37 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.4488</v>
+        <v>1.0072</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4438</v>
+        <v>0.9693000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>0.005</v>
+        <v>0.0378</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7806999999999999</v>
+        <v>0.7785</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7806999999999999</v>
+        <v>0.7785</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7966</v>
+        <v>0.7929</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7966</v>
+        <v>0.7929</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0159</v>
+        <v>-0.0144</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0159</v>
+        <v>-0.0144</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6681</v>
+        <v>0.2287</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6472</v>
+        <v>0.1765</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0209</v>
+        <v>0.0523</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5252</v>
+        <v>0.7986</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0485</v>
+        <v>1.1466</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5232</v>
+        <v>-0.3479</v>
       </c>
       <c r="G19" t="n">
-        <v>2.7278</v>
+        <v>2.7429</v>
       </c>
       <c r="H19" t="n">
-        <v>1.0112</v>
+        <v>1.03</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7166</v>
+        <v>1.7129</v>
       </c>
       <c r="J19" t="n">
-        <v>1.8253</v>
+        <v>1.8091</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9351</v>
+        <v>0.9308</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8902</v>
+        <v>0.8783</v>
       </c>
       <c r="M19" t="n">
-        <v>0.9025</v>
+        <v>0.9338</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0761</v>
+        <v>0.0993</v>
       </c>
       <c r="O19" t="n">
-        <v>0.8264</v>
+        <v>0.8345</v>
       </c>
       <c r="P19" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.8733</v>
+        <v>-1.6351</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9376</v>
+        <v>-0.8204</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.9358</v>
+        <v>-0.8147</v>
       </c>
       <c r="V19" t="n">
-        <v>-3.278</v>
+        <v>-3.2684</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X19" t="n">
-        <v>-3.4387</v>
+        <v>-3.4262</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. SHERMADINI</t>
+          <t>B. FITIPALDO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4174</v>
+        <v>0.7025</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.3225</v>
+        <v>-2.0592</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7399</v>
+        <v>2.7616</v>
       </c>
       <c r="G20" t="n">
-        <v>1.2778</v>
+        <v>0.2912</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8326</v>
+        <v>0.232</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4452</v>
+        <v>0.0591</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8104</v>
+        <v>-0.9032</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6611</v>
+        <v>-0.8726</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1493</v>
+        <v>-0.0307</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4674</v>
+        <v>1.1944</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1715</v>
+        <v>1.1046</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2959</v>
+        <v>0.0898</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.6805</v>
+        <v>1.8211</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5878</v>
+        <v>2.9592</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.4333</v>
+        <v>-1.9545</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1179</v>
+        <v>-0.5625</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.3153</v>
+        <v>-1.392</v>
       </c>
       <c r="V20" t="n">
-        <v>1.2534</v>
+        <v>0.5447</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2534</v>
+        <v>0.5447</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B. FITIPALDO</t>
+          <t>G. SHERMADINI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1284</v>
+        <v>0.4552</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2598</v>
+        <v>-0.5891999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>2.1315</v>
+        <v>1.0445</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2898</v>
+        <v>1.2834</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2206</v>
+        <v>0.8302</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0692</v>
+        <v>0.4532</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.8736</v>
+        <v>0.7932</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.8627</v>
+        <v>0.6443</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.0108</v>
+        <v>0.1489</v>
       </c>
       <c r="M21" t="n">
-        <v>1.1634</v>
+        <v>0.4901</v>
       </c>
       <c r="N21" t="n">
-        <v>1.0833</v>
+        <v>0.1859</v>
       </c>
       <c r="O21" t="n">
-        <v>0.08</v>
+        <v>0.3043</v>
       </c>
       <c r="P21" t="n">
-        <v>1.8147</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R21" t="n">
-        <v>2.9488</v>
+        <v>1.5934</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.7792</v>
+        <v>-1.3925</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7984</v>
+        <v>-0.3534</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.9807</v>
+        <v>-1.0391</v>
       </c>
       <c r="V21" t="n">
-        <v>0.5463</v>
+        <v>1.2472</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5463</v>
+        <v>1.2472</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2125,40 +2125,40 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.7286</v>
+        <v>-0.5804</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8908</v>
+        <v>-0.7761</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1622</v>
+        <v>0.1958</v>
       </c>
       <c r="G22" t="n">
         <v>-0.2958</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4531</v>
+        <v>-0.4538</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.7517</v>
+        <v>-0.7552</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.7517</v>
+        <v>-0.7552</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4559</v>
+        <v>0.4593</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2986</v>
+        <v>0.3014</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4328</v>
+        <v>-0.2845</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1391</v>
+        <v>-0.021</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2937</v>
+        <v>-0.2636</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.0089</v>
+        <v>-0.9819</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7604</v>
+        <v>-0.7725</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2484</v>
+        <v>-0.2094</v>
       </c>
       <c r="G23" t="n">
         <v>1.3116</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.0318</v>
+        <v>-0.0289</v>
       </c>
       <c r="I23" t="n">
-        <v>1.3434</v>
+        <v>1.3405</v>
       </c>
       <c r="J23" t="n">
-        <v>1.7166</v>
+        <v>1.7129</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1.7166</v>
+        <v>1.7129</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.405</v>
+        <v>-0.4012</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0318</v>
+        <v>-0.0289</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3451</v>
+        <v>-0.3148</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2087</v>
+        <v>-0.2091</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1364</v>
+        <v>-0.1057</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>T. ABROMAITIS</t>
+          <t>M. HUERTAS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.1363</v>
+        <v>-1.6256</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.8822</v>
+        <v>-2.9004</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.2542</v>
+        <v>1.2748</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.2556</v>
+        <v>1.1394</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1442</v>
+        <v>0.627</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3998</v>
+        <v>0.5123</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.2561</v>
+        <v>0.3622</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.4054</v>
+        <v>0.1542</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1493</v>
+        <v>0.2081</v>
       </c>
       <c r="M24" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.7771</v>
       </c>
       <c r="N24" t="n">
-        <v>0.5496</v>
+        <v>0.4729</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.549</v>
+        <v>0.3043</v>
       </c>
       <c r="P24" t="n">
-        <v>0.9073</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-3.4145</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9073</v>
+        <v>1.8211</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6028</v>
+        <v>-1.0137</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6261</v>
+        <v>-0.3929</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0233</v>
+        <v>-0.6209</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.1853</v>
+        <v>-0.1578</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.1853</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>M. HUERTAS</t>
+          <t>T. ABROMAITIS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.1742</v>
+        <v>-1.9825</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.1951</v>
+        <v>-0.5335</v>
       </c>
       <c r="F25" t="n">
-        <v>1.0209</v>
+        <v>-1.4491</v>
       </c>
       <c r="G25" t="n">
-        <v>1.1583</v>
+        <v>-0.2439</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6438</v>
+        <v>0.1491</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5144</v>
+        <v>-0.393</v>
       </c>
       <c r="J25" t="n">
-        <v>0.4081</v>
+        <v>-0.2615</v>
       </c>
       <c r="K25" t="n">
-        <v>0.1896</v>
+        <v>-0.4104</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2185</v>
+        <v>0.1489</v>
       </c>
       <c r="M25" t="n">
-        <v>0.7502</v>
+        <v>0.0176</v>
       </c>
       <c r="N25" t="n">
-        <v>0.4542</v>
+        <v>0.5595</v>
       </c>
       <c r="O25" t="n">
-        <v>0.2959</v>
+        <v>-0.5419</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.5878</v>
+        <v>0.9105</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.4025</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.8147</v>
+        <v>0.9105</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.5839</v>
+        <v>-0.4703</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.747</v>
+        <v>-0.272</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.8369</v>
+        <v>-0.1983</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.1607</v>
+        <v>-2.1789</v>
       </c>
       <c r="W25" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.7071</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>8.529199999999999</v>
+        <v>10.1099</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.1775000000000002</v>
+        <v>-0.4740000000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>8.706899999999999</v>
+        <v>10.5839</v>
       </c>
       <c r="G26" t="n">
-        <v>15.2475</v>
+        <v>15.2717</v>
       </c>
       <c r="H26" t="n">
-        <v>6.211199999999999</v>
+        <v>6.244899999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>9.036</v>
+        <v>9.026499999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>9.080099999999998</v>
+        <v>8.863</v>
       </c>
       <c r="K26" t="n">
-        <v>0.6442000000000001</v>
+        <v>0.5099999999999997</v>
       </c>
       <c r="L26" t="n">
-        <v>8.4359</v>
+        <v>8.3529</v>
       </c>
       <c r="M26" t="n">
-        <v>6.1675</v>
+        <v>6.408499999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>5.567000000000001</v>
+        <v>5.734999999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>0.6003000000000001</v>
+        <v>0.6735</v>
       </c>
       <c r="P26" t="n">
-        <v>5.6708</v>
+        <v>5.690800000000001</v>
       </c>
       <c r="Q26" t="n">
-        <v>-13.6099</v>
+        <v>-13.6579</v>
       </c>
       <c r="R26" t="n">
-        <v>19.2807</v>
+        <v>19.3487</v>
       </c>
       <c r="S26" t="n">
-        <v>-12.8389</v>
+        <v>-11.311</v>
       </c>
       <c r="T26" t="n">
-        <v>-4.3249</v>
+        <v>-4.323700000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>-8.5139</v>
+        <v>-6.987399999999999</v>
       </c>
       <c r="V26" t="n">
-        <v>0.4499000000000002</v>
+        <v>0.4583000000000004</v>
       </c>
       <c r="W26" t="n">
-        <v>8.677100000000001</v>
+        <v>8.644300000000001</v>
       </c>
       <c r="X26" t="n">
-        <v>-8.2273</v>
+        <v>-8.1859</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104529_W8.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104529_W8.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.2667</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104529_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104529_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104529_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104529_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104529_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104529_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104529_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-2.4457</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104529_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.1984</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104529_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104529_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104529_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-8.6442</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104529_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104529_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104529_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104529_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104529_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-3.4262</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104529_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104529_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104529_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104529_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104529_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104529_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104529_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-8.1859</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
